--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/3.4 Product Backlog.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/3.4 Product Backlog.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="106">
   <si>
     <t>Desarrollo ágil: Pila de Producto (Product Backlog)</t>
   </si>
@@ -61,15 +61,15 @@
     <t>Iteración (Sprint)</t>
   </si>
   <si>
-    <t>Prioridad</t>
-  </si>
-  <si>
     <t>Identifica los posibles estados de la historia durante su ciclo de vida:
 - Vacío: La historia fue identifica pero aún no ha sido asignada a una iteración.
 - Planificada: La historia fue asignada a una iteración y aún no ha comenzado su ejecución. Puede tener este estado incluyendo en la iteración donde está planificado ejecutarla (pero que aún no ha comenzado).
 - En Proceso: La historia fue seleccionada por el equipo y está en proceso de desarrollo (en ejecución).
 - Hecho (Donde): La historia fue desarrollada. Es importante clarificar la definición de “Hecho” con el equipo de trabajo. “Hecho” no sólo incluye el desarrollo sino la integración y pruebas integrales del Software. Una historia hecha puede presentarse al dueño de producto para sus pruebas de aceptación.
 - Descartada: Se determinó que la historia ya no es relevante, su contenido se incluyó en otro grupo de historias o fue cancelada.</t>
+  </si>
+  <si>
+    <t>Prioridad</t>
   </si>
   <si>
     <t>Comentarios</t>
@@ -84,10 +84,10 @@
     <t>HIU-EP1-001</t>
   </si>
   <si>
-    <t>Como un usuario registrado, necesito iniciar sesión en la plataforma utilizando mis credenciales, con la finalidad de acceder de forma segura a las funcionalidades correspondientes a mi rol</t>
+    <t>Siguiendo el marco de trabajo ágil y Scrum, se le deben asignar prioridades a las historias, según las instrucciones del dueño de producto (ProductOwner). De esta forma pueden ordenarse. Las historias de mayor prioridad deben ser las que agregan más valor al negocio, y deben ser originadas en sus necesidades.</t>
   </si>
   <si>
-    <t>Siguiendo el marco de trabajo ágil y Scrum, se le deben asignar prioridades a las historias, según las instrucciones del dueño de producto (ProductOwner). De esta forma pueden ordenarse. Las historias de mayor prioridad deben ser las que agregan más valor al negocio, y deben ser originadas en sus necesidades.</t>
+    <t>Como un usuario registrado, necesito iniciar sesión en la plataforma utilizando mis credenciales, con la finalidad de acceder de forma segura a las funcionalidades correspondientes a mi rol</t>
   </si>
   <si>
     <t>Iniciar sesión en la plataforma</t>
@@ -96,7 +96,7 @@
     <t>Comentarios o detalles relacionadas que expliquen la historia. Para definiciones de mayor longitud deben usarse documentos externos, por ejemplo la plantilla de historias de usuario.</t>
   </si>
   <si>
-    <t>Planificada</t>
+    <t>Hecho</t>
   </si>
   <si>
     <t>Sprint 1</t>
@@ -111,7 +111,7 @@
     <t>HIU-EP1-002</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito acceder a las funcionalidades permitidas según mis permisos, con la finalidad de utilizar únicamente las funcionalidades que tengo autorizadas</t>
+    <t>Como un usuario autenticado, necesito acceder a las funcionalidades permitidas según mis permisos, con la finalidad de utilizar únicamente las funcionalidades que tengo autorizadas</t>
   </si>
   <si>
     <t>Control de acceso según rol</t>
@@ -123,7 +123,7 @@
     <t>HIU-EP2-001</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito consultar el estado y ubicación actual de las cajas quirúrgicas, con la finalidad de conocer oportunamente dónde se encuentra y en qué etapa del proceso está cada caja</t>
+    <t>Como operador, necesito consultar el estado y ubicación actual de las cajas quirúrgicas, con la finalidad de conocer oportunamente dónde se encuentra y en qué etapa del proceso está cada caja</t>
   </si>
   <si>
     <t>Consulta de estado y ubicación de cajas quirúrgicas</t>
@@ -135,7 +135,7 @@
     <t>HIU-EP2-002</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito registrar el cambio de etapa de una caja quirúrgica, con la finalidad de mantener actualizada su trazabilidad durante el proceso de esterilización</t>
+    <t>Como operador, necesito registrar el cambio de etapa de una caja quirúrgica, con la finalidad de mantener actualizada su trazabilidad durante el proceso de esterilización</t>
   </si>
   <si>
     <t>Registro de cambio de etapa de cajas quirúrgicas</t>
@@ -147,7 +147,7 @@
     <t>HIU-EP2-003</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito retroceder una caja quirúrgica a una etapa anterior cuando corresponda, con la finalidad de corregir su recorrido y asegurar que complete correctamente el proceso de esterilización</t>
+    <t>Como operador, necesito retroceder una caja quirúrgica a una etapa anterior cuando corresponda, con la finalidad de corregir su recorrido y asegurar que complete correctamente el proceso de esterilización</t>
   </si>
   <si>
     <t>Retroceder etapa</t>
@@ -171,7 +171,7 @@
     <t>HIU-EP5-001</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito registrar la entrega de una caja quirúrgica o material a un servicio, con la finalidad de dejar constancia de la entrega y de los responsables involucrados</t>
+    <t>Como operador, necesito registrar la entrega de una caja quirúrgica o material a un servicio, con la finalidad de dejar constancia de la entrega y de los responsables involucrados</t>
   </si>
   <si>
     <t>Registro de entrega de cajas quirúrgicas y materiales</t>
@@ -183,7 +183,7 @@
     <t>HIU-EP4-001</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito consultar el catálogo digital de cajas quirúrgicas, con la finalidad de conocer las cajas registradas y localizar aquellas pertenecientes a un servicio específico</t>
+    <t>Como operador, necesito consultar el catálogo digital de cajas quirúrgicas, con la finalidad de conocer las cajas registradas y localizar aquellas pertenecientes a un servicio específico</t>
   </si>
   <si>
     <t>Consulta del catálogo digital de cajas quirúrgicas</t>
@@ -198,7 +198,7 @@
     <t>HIU-EP2-004</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito registrar el proceso o actividad específica en que se encuentra una caja dentro de su etapa actual, con la finalidad de conocer detalladamente su avance y mantener actualizada su trazabilidad durante el proceso de esterilización</t>
+    <t>Como operador, necesito registrar el proceso o actividad específica en que se encuentra una caja dentro de su etapa actual, con la finalidad de conocer detalladamente su avance y mantener actualizada su trazabilidad durante el proceso de esterilización</t>
   </si>
   <si>
     <t>Registrar actividad de la etapa</t>
@@ -213,10 +213,13 @@
     <t>HIU-EP4-002</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito consultar la ficha detallada de una caja quirúrgica, con la finalidad de conocer los instrumentos y materiales que debe contener y disponer de una guía visual para su identificación</t>
+    <t>Como operador, necesito consultar la ficha detallada de una caja quirúrgica, con la finalidad de conocer los instrumentos y materiales que debe contener y disponer de una guía visual para su identificación</t>
   </si>
   <si>
     <t>Consulta detallada de las cajas quirúrgicas</t>
+  </si>
+  <si>
+    <t>En Proceso</t>
   </si>
   <si>
     <t>La ficha mostrará la información de la caja, sus materiales e instrumental. Cuando corresponda, incluirá una guía visual o indicará que no está disponible.</t>
@@ -225,7 +228,7 @@
     <t>HIU-EP3-002</t>
   </si>
   <si>
-    <t>Como un usuario autorizado, necesito registrar los movimientos de los elementos de un inventario, con la finalidad de mantener actualizadas las cantidades disponibles y conservar un registro de sus variaciones</t>
+    <t>Como administradora o enfermera, necesito registrar los movimientos de los elementos de un inventario, con la finalidad de mantener actualizadas las cantidades disponibles y conservar un registro de sus variaciones</t>
   </si>
   <si>
     <t>Registrar salida de insumos</t>
@@ -240,7 +243,7 @@
     <t>HIU-EP3-004</t>
   </si>
   <si>
-    <t>Como una enfermera de turno y/o jefatura del servicio, necesito registrar la reposición de los elementos del inventario, con la finalidad de actualizar las existencias disponibles y mantener el control de los elementos repuestos</t>
+    <t>Como administradora, necesito registrar la reposición de los elementos del inventario, con la finalidad de actualizar las existencias disponibles y mantener el control de los elementos repuestos</t>
   </si>
   <si>
     <t>Registrar reposición de insumos</t>
@@ -252,10 +255,13 @@
     <t>HIU-EP1-003</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito gestionar las cuentas de los usuarios y asignarles roles, con la finalidad de mantener actualizados los usuarios autorizados de la plataforma</t>
+    <t>Como administradora, necesito gestionar las cuentas de los usuarios y asignarles roles, con la finalidad de mantener actualizados los usuarios autorizados de la plataforma</t>
   </si>
   <si>
     <t>Gestión de usuarios y roles</t>
+  </si>
+  <si>
+    <t>Planificada</t>
   </si>
   <si>
     <t>Sprint 3</t>
@@ -267,7 +273,7 @@
     <t>HIU-EP1-004</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito consultar el registro de auditoría de las acciones realizadas por los usuarios, con la finalidad de supervisar las actividades efectuadas dentro de la plataforma</t>
+    <t>Como administradora, necesito consultar el registro de auditoría de las acciones realizadas por los usuarios, con la finalidad de supervisar las actividades efectuadas dentro de la plataforma</t>
   </si>
   <si>
     <t>Consulta de auditoría</t>
@@ -279,7 +285,7 @@
     <t>HIU-EP3-003</t>
   </si>
   <si>
-    <t>Como una enfermera de turno y/o jefatura del servicio, necesito configurar el nivel de existencias que generará una alerta para cada elemento, con la finalidad de recibir una advertencia cuando sea necesario gestionar su reposición</t>
+    <t>Como enfermera, necesito configurar el nivel de existencias que generará una alerta para cada elemento, con la finalidad de recibir una advertencia cuando sea necesario gestionar su reposición</t>
   </si>
   <si>
     <t>Configurar alertas de inventario</t>
@@ -291,7 +297,7 @@
     <t>HIU-EP4-003</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito crear, modificar y retirar cajas quirúrgicas del catálogo digital, con la finalidad de mantener actualizada la información, el contenido y las guías visuales de las cajas registradas</t>
+    <t>Como administradora, necesito crear, modificar y retirar cajas quirúrgicas del catálogo digital, con la finalidad de mantener actualizada la información, el contenido y las guías visuales de las cajas registradas</t>
   </si>
   <si>
     <t>Funcionalidad agregar cajas quirúrgicas</t>
@@ -303,7 +309,7 @@
     <t>HIU-EP5-002</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito consultar el historial de entregas de las cajas quirúrgicas y sus responsables, con la finalidad de verificar las entregas realizadas y conocer quién participó en cada entrega y recepción</t>
+    <t>Como administradora o enfermera, necesito consultar el historial de entregas de las cajas quirúrgicas y sus responsables, con la finalidad de verificar las entregas realizadas y conocer quién participó en cada entrega y recepción</t>
   </si>
   <si>
     <t>Historial de entregas de cajas quirúrgicas y materiales</t>
@@ -315,7 +321,7 @@
     <t>HIU-EP6-001</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito consultar las estadísticas de producción de la central, con la finalidad de conocer el volumen de material procesado durante el período seleccionado</t>
+    <t>Como administradora o secretaria, necesito consultar las estadísticas de producción de la central, con la finalidad de conocer el volumen de material procesado durante el período seleccionado</t>
   </si>
   <si>
     <t>Consulta de estadísticas de producción de la Central</t>
@@ -327,7 +333,7 @@
     <t>HIU-EP6-002</t>
   </si>
   <si>
-    <t>Como jefatura del servicio, necesito generar reportes de producción de la central, con la finalidad de disponer de información consolidada para su revisión y entrega</t>
+    <t>Como administradora o secretaria, necesito generar reportes de producción de la central, con la finalidad de disponer de información consolidada para su revisión y entrega</t>
   </si>
   <si>
     <t>Generación de reportes de producción de la Central</t>
@@ -442,6 +448,20 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
@@ -460,20 +480,6 @@
       <bottom/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
       <left/>
       <right/>
       <bottom/>
@@ -482,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -505,23 +511,26 @@
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
@@ -529,43 +538,46 @@
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -838,10 +850,10 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="12"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -866,10 +878,10 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="14"/>
+      <c r="F3" s="15"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="15"/>
+      <c r="I3" s="16"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -909,7 +921,7 @@
         <v>13</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="19" t="s">
         <v>16</v>
@@ -937,8 +949,8 @@
       <c r="B5" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>20</v>
+      <c r="C5" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>22</v>
@@ -981,7 +993,7 @@
       <c r="B6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="22" t="s">
@@ -1025,7 +1037,7 @@
       <c r="B7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="22" t="s">
@@ -1069,7 +1081,7 @@
       <c r="B8" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="22" t="s">
@@ -1113,7 +1125,7 @@
       <c r="B9" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D9" s="22" t="s">
@@ -1163,7 +1175,7 @@
       <c r="D10" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="25">
@@ -1201,13 +1213,13 @@
       <c r="B11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="28" t="s">
         <v>49</v>
       </c>
       <c r="D11" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="23" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="25">
@@ -1245,13 +1257,13 @@
       <c r="B12" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="23" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="25">
@@ -1289,13 +1301,13 @@
       <c r="B13" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="28" t="s">
         <v>58</v>
       </c>
       <c r="D13" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="29" t="s">
         <v>24</v>
       </c>
       <c r="F13" s="25">
@@ -1333,14 +1345,14 @@
       <c r="B14" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="28" t="s">
         <v>63</v>
       </c>
       <c r="D14" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="25" t="s">
-        <v>24</v>
+      <c r="E14" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="F14" s="25">
         <v>5.0</v>
@@ -1352,7 +1364,7 @@
         <v>55</v>
       </c>
       <c r="I14" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J14" s="20"/>
       <c r="K14" s="1"/>
@@ -1375,16 +1387,16 @@
     <row r="15" ht="69.0" customHeight="1">
       <c r="A15" s="21"/>
       <c r="B15" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="C15" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="25" t="s">
-        <v>24</v>
+      <c r="D15" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="F15" s="25">
         <v>3.0</v>
@@ -1393,10 +1405,10 @@
         <v>60</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I15" s="27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J15" s="20"/>
       <c r="K15" s="1"/>
@@ -1419,16 +1431,16 @@
     <row r="16" ht="69.0" customHeight="1">
       <c r="A16" s="21"/>
       <c r="B16" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="C16" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>24</v>
+      <c r="D16" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="F16" s="25">
         <v>4.0</v>
@@ -1437,10 +1449,10 @@
         <v>60</v>
       </c>
       <c r="H16" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I16" s="27" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J16" s="20"/>
       <c r="K16" s="1"/>
@@ -1463,28 +1475,28 @@
     <row r="17" ht="69.0" customHeight="1">
       <c r="A17" s="21"/>
       <c r="B17" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="C17" s="14" t="s">
         <v>77</v>
       </c>
+      <c r="D17" s="22" t="s">
+        <v>78</v>
+      </c>
       <c r="E17" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F17" s="22">
         <v>3.0</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H17" s="23" t="s">
         <v>55</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J17" s="20"/>
       <c r="K17" s="1"/>
@@ -1507,28 +1519,28 @@
     <row r="18" ht="69.0" customHeight="1">
       <c r="A18" s="21"/>
       <c r="B18" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>81</v>
+      <c r="C18" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F18" s="22">
         <v>3.0</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H18" s="23" t="s">
         <v>55</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J18" s="20"/>
       <c r="K18" s="1"/>
@@ -1551,28 +1563,28 @@
     <row r="19" ht="69.0" customHeight="1">
       <c r="A19" s="21"/>
       <c r="B19" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>85</v>
+      <c r="C19" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F19" s="22">
         <v>4.0</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J19" s="20"/>
       <c r="K19" s="1"/>
@@ -1595,28 +1607,28 @@
     <row r="20" ht="69.0" customHeight="1">
       <c r="A20" s="21"/>
       <c r="B20" s="22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>89</v>
+      <c r="C20" s="30" t="s">
+        <v>91</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F20" s="22">
         <v>4.0</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J20" s="20"/>
       <c r="K20" s="1"/>
@@ -1639,28 +1651,28 @@
     <row r="21" ht="69.0" customHeight="1">
       <c r="A21" s="21"/>
       <c r="B21" s="22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>93</v>
+      <c r="C21" s="30" t="s">
+        <v>95</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F21" s="22">
         <v>2.0</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J21" s="20"/>
       <c r="K21" s="1"/>
@@ -1683,28 +1695,28 @@
     <row r="22" ht="69.0" customHeight="1">
       <c r="A22" s="21"/>
       <c r="B22" s="22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>97</v>
+      <c r="C22" s="30" t="s">
+        <v>99</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F22" s="22">
         <v>8.0</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J22" s="20"/>
       <c r="K22" s="1"/>
@@ -1727,28 +1739,28 @@
     <row r="23" ht="69.0" customHeight="1">
       <c r="A23" s="21"/>
       <c r="B23" s="22" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
-      <c r="C23" s="28" t="s">
-        <v>101</v>
+      <c r="C23" s="30" t="s">
+        <v>103</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="F23" s="22">
         <v>4.0</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J23" s="20"/>
       <c r="K23" s="1"/>
@@ -1770,14 +1782,14 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -29248,10 +29260,10 @@
     </row>
     <row r="4" ht="27.75" customHeight="1">
       <c r="A4" s="2"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="2"/>
@@ -29280,10 +29292,10 @@
     </row>
     <row r="5" ht="59.25" customHeight="1">
       <c r="A5" s="2"/>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2"/>
@@ -29312,10 +29324,10 @@
     </row>
     <row r="6" ht="65.25" customHeight="1">
       <c r="A6" s="2"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2"/>
@@ -29344,10 +29356,10 @@
     </row>
     <row r="7" ht="64.5" customHeight="1">
       <c r="A7" s="2"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="2"/>
@@ -29376,11 +29388,11 @@
     </row>
     <row r="8" ht="181.5" customHeight="1">
       <c r="A8" s="2"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>15</v>
+      <c r="C8" s="14" t="s">
+        <v>14</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -29408,10 +29420,10 @@
     </row>
     <row r="9" ht="63.0" customHeight="1">
       <c r="A9" s="2"/>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2"/>
@@ -29440,10 +29452,10 @@
     </row>
     <row r="10" ht="75.0" customHeight="1">
       <c r="A10" s="2"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
@@ -29472,11 +29484,11 @@
     </row>
     <row r="11" ht="72.75" customHeight="1">
       <c r="A11" s="2"/>
-      <c r="B11" s="13" t="s">
-        <v>14</v>
+      <c r="B11" s="11" t="s">
+        <v>15</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>21</v>
+      <c r="C11" s="11" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -29504,10 +29516,10 @@
     </row>
     <row r="12" ht="51.0" customHeight="1">
       <c r="A12" s="2"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="2"/>
